--- a/input/sample.xlsx
+++ b/input/sample.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">First_Name </t>
   </si>
@@ -43,18 +43,63 @@
     <t xml:space="preserve">Summary </t>
   </si>
   <si>
+    <t xml:space="preserve">Job_Title1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Company1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Employement_Date1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Job_Summary1</t>
   </si>
   <si>
+    <t xml:space="preserve">Job_Title2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Company2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Employement_Date2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Job_Summary2</t>
   </si>
   <si>
+    <t xml:space="preserve">Job_Title3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Company3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Employement_Date3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Job_Summary3</t>
   </si>
   <si>
+    <t xml:space="preserve">Job_Title4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Company4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Employement_Date4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Job_Summary4</t>
   </si>
   <si>
+    <t xml:space="preserve">Job_Title5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Company5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job_Employement_Date5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Job_Summary5</t>
   </si>
   <si>
@@ -86,6 +131,15 @@
   </si>
   <si>
     <t xml:space="preserve">Senior Java Developer with over 15 years of experience designing, developing, and maintaining enterprise-grade applications. Strong expertise in Java, Spring ecosystem, microservices architecture, and cloud-native solutions. Proven track record in leading development teams, optimizing system performance, and delivering scalable, secure, and high-availability systems. Adept at translating business requirements into technical solutions and driving continuous improvement through best practices, code quality, and automation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Java Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABC Tech Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January 2018 – Present</t>
   </si>
   <si>
     <r>
@@ -94,8 +148,9 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Senior Java Developer
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -104,8 +159,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ABC Tech Solutions
-January 2018 – Present
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
 Lead the design and development of microservices-based applications using Spring Boot and REST APIs 
 Architected scalable backend systems deployed on AWS, improving system uptime to 99.9% 
 Mentored junior developers and conducted code reviews to ensure adherence to best practices 
@@ -115,14 +179,24 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Java Developer / Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XYZ Innovations Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">June 2010 – December 2017</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Java Developer / Software Engineer
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -130,9 +204,9 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">XYZ Innovations Inc.
-June 2010 – December 2017
+      <t xml:space="preserve">
 Developed and maintained enterprise web applications using Java EE, Spring MVC, and Hibernate 
 Optimized database queries and application performance, reducing response time by 30% 
 Participated in full software development lifecycle (SDLC) including requirements analysis and deployment 
@@ -148,6 +222,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Bachelor of Science in Computer Science
 </t>
@@ -157,6 +232,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">University of the Philippines
 2006 – 2010 </t>
@@ -168,82 +244,27 @@
 Scrum Master Certified (SMC)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Java, SQL, JavaScript, Spring Boot, Spring MVC, Hibernate, JPA</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Microservices, RESTful APIs, Event-Driven Architecture</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Git, Jenkins, Docker, Kubernetes, AWS (EC2, S3, RDS, Lambda)</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MySQL, PostgreSQL, Oracle</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">CI/CD, Agile/Scrum, Unit Testing (JUnit, Mockito)</t>
-    </r>
+    <t xml:space="preserve">Java
+SQL
+JavaScript
+Spring Boot
+Spring MVC
+Hibernate
+JPA
+Microservices
+RESTful APIs
+Event-Driven Architecture
+Git
+Jenkins
+Docker
+Kubernetes
+AWS (EC2, S3, RDS, Lambda)
+MySQL
+PostgreSQL
+Oracle
+CI/CD
+Agile/Scrum
+Unit Testing (JUnit, Mockito)</t>
   </si>
 </sst>
 </file>
@@ -254,11 +275,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -279,12 +301,14 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -293,10 +317,23 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -341,40 +378,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -501,110 +550,197 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="67.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="62.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="57.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="13.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="14.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="13.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="34.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="29.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="52.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="67.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="17.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="21.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="62.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="17.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="21.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="57.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="17.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="21.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="3" width="13.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="17.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="2" width="21.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="3" width="14.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="24.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="2" width="17.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="2" width="21.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="3" width="13.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="3" width="34.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="3" width="29.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="3" width="30.74"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" s="5" customFormat="true" ht="173.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>26</v>
+    <row r="2" s="6" customFormat="true" ht="239.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
